--- a/data/trans_orig/P1429-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2007</t>
+          <t>Población con diagnóstico de osteoporosis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24565</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>47783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675009</t>
+          <t>676805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689291</t>
+          <t>690023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652639</t>
+          <t>652325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671967</t>
+          <t>671807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334835</t>
+          <t>1334580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357798</t>
+          <t>1357846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>50435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36788</t>
+          <t>37163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>940667</t>
+          <t>940402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>954850</t>
+          <t>954645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917952</t>
+          <t>917958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>942322</t>
+          <t>942142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1865800</t>
+          <t>1864641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1893405</t>
+          <t>1893030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28461</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52147</t>
+          <t>53262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670944</t>
+          <t>670986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677759</t>
+          <t>677758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631694</t>
+          <t>630579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655380</t>
+          <t>655679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305572</t>
+          <t>1306584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1331060</t>
+          <t>1332076</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32187</t>
+          <t>33258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40731</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69860</t>
+          <t>69209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>926229</t>
+          <t>925938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938084</t>
+          <t>937449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>980338</t>
+          <t>979670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1006425</t>
+          <t>1005354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1910974</t>
+          <t>1911625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1940103</t>
+          <t>1940532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122035</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169587</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>153714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206337</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3230763</t>
+          <t>3228267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3253340</t>
+          <t>3251746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3209610</t>
+          <t>3210105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3257162</t>
+          <t>3258051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6449404</t>
+          <t>6447968</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6500167</t>
+          <t>6502027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2012</t>
+          <t>Población con diagnóstico de osteoporosis en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696221</t>
+          <t>696181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>666184</t>
+          <t>667896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685101</t>
+          <t>686259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1368413</t>
+          <t>1368843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1387979</t>
+          <t>1387905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50600</t>
+          <t>53019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51133</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1015861</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978373</t>
+          <t>975954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1003177</t>
+          <t>1003030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1995788</t>
+          <t>1993725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2020689</t>
+          <t>2019903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>745250</t>
+          <t>743128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>736534</t>
+          <t>737769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>757994</t>
+          <t>758695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1489761</t>
+          <t>1491753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513500</t>
+          <t>1514252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44783</t>
+          <t>48259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>78659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80430</t>
+          <t>79964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>941538</t>
+          <t>941561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975600</t>
+          <t>973242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1007118</t>
+          <t>1003642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919210</t>
+          <t>1919676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951295</t>
+          <t>1950863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120743</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169238</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125074</t>
+          <t>123147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175682</t>
+          <t>174630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3410313</t>
+          <t>3410664</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3423699</t>
+          <t>3423719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3384752</t>
+          <t>3383564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3433247</t>
+          <t>3434752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6804084</t>
+          <t>6805136</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6854692</t>
+          <t>6856619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2016</t>
+          <t>Población con diagnóstico de osteoporosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39329</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>42845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666955</t>
+          <t>667739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633510</t>
+          <t>634227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655601</t>
+          <t>655015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1305996</t>
+          <t>1304794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1328705</t>
+          <t>1328461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>49462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55104</t>
+          <t>54626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1012802</t>
+          <t>1012842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021516</t>
+          <t>1021248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>993046</t>
+          <t>993451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1019223</t>
+          <t>1018996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2010240</t>
+          <t>2010718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036680</t>
+          <t>2037453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46260</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>750339</t>
+          <t>751996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>741274</t>
+          <t>739684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764668</t>
+          <t>764090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1498303</t>
+          <t>1497741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522026</t>
+          <t>1523351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>41074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927972</t>
+          <t>928189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936568</t>
+          <t>936562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002379</t>
+          <t>1002705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024030</t>
+          <t>1024633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933567</t>
+          <t>1935708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1958523</t>
+          <t>1959092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>101099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150165</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111233</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159405</t>
+          <t>159314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3374435</t>
+          <t>3374298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3388129</t>
+          <t>3388346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3394377</t>
+          <t>3396560</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3443933</t>
+          <t>3443443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6779487</t>
+          <t>6779578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6827659</t>
+          <t>6826664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2023</t>
+          <t>Población con diagnóstico de osteoporosis en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49052</t>
+          <t>49011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36082</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56090</t>
+          <t>57388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623754</t>
+          <t>623743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632115</t>
+          <t>631959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625718</t>
+          <t>625759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>643489</t>
+          <t>643914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1254122</t>
+          <t>1252824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1274130</t>
+          <t>1273474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49174</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61404</t>
+          <t>60219</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1177290</t>
+          <t>1176952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1188466</t>
+          <t>1188428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>904087</t>
+          <t>903483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921048</t>
+          <t>921162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2083400</t>
+          <t>2084585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2112427</t>
+          <t>2112438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>45647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47159</t>
+          <t>47929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>691841</t>
+          <t>692039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699636</t>
+          <t>699684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>885239</t>
+          <t>884126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914947</t>
+          <t>914746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1583782</t>
+          <t>1583012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1607745</t>
+          <t>1608504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>26724</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63291</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>47739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76071</t>
+          <t>75605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897601</t>
+          <t>897907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920826</t>
+          <t>920686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1026245</t>
+          <t>1027047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1051333</t>
+          <t>1052147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938096</t>
+          <t>1938562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966336</t>
+          <t>1966428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130962</t>
+          <t>133684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183702</t>
+          <t>182674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>162971</t>
+          <t>160015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215511</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3408021</t>
+          <t>3407087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3433643</t>
+          <t>3433058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3463638</t>
+          <t>3464666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3516378</t>
+          <t>3513656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6911350</t>
+          <t>6911351</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6884612</t>
+          <t>6887193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6937152</t>
+          <t>6940109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P1429-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676805</t>
+          <t>676508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>690023</t>
+          <t>690149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652325</t>
+          <t>651120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671807</t>
+          <t>671832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334580</t>
+          <t>1333791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357846</t>
+          <t>1357593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26251</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37163</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>64251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>940402</t>
+          <t>940319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>954645</t>
+          <t>955500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917958</t>
+          <t>918264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>942142</t>
+          <t>943181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1864641</t>
+          <t>1865942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1893030</t>
+          <t>1893246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28162</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>52358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30274</t>
+          <t>30448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670986</t>
+          <t>671276</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677758</t>
+          <t>677755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630579</t>
+          <t>631483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655679</t>
+          <t>655345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306584</t>
+          <t>1304866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1332076</t>
+          <t>1331902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33258</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58942</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69209</t>
+          <t>68175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925938</t>
+          <t>925961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937449</t>
+          <t>937440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>979670</t>
+          <t>978871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005354</t>
+          <t>1005689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1911625</t>
+          <t>1912659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1940532</t>
+          <t>1940445</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169092</t>
+          <t>169876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153714</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3228267</t>
+          <t>3229859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3251746</t>
+          <t>3252419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3210105</t>
+          <t>3209321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3258051</t>
+          <t>3257656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6447968</t>
+          <t>6449611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6502027</t>
+          <t>6500686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29154</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696181</t>
+          <t>696259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667896</t>
+          <t>667321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>686259</t>
+          <t>685617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1368843</t>
+          <t>1366048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1387905</t>
+          <t>1386878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53019</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>26191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>49104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>975954</t>
+          <t>978777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1003030</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993725</t>
+          <t>1997817</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2019903</t>
+          <t>2020730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743128</t>
+          <t>743449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>737769</t>
+          <t>736711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>758695</t>
+          <t>757650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1491753</t>
+          <t>1489789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1514252</t>
+          <t>1513835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>49024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79964</t>
+          <t>79928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>941561</t>
+          <t>939718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>973242</t>
+          <t>971422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003642</t>
+          <t>1005467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919676</t>
+          <t>1919712</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1950863</t>
+          <t>1950616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170426</t>
+          <t>170831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>124345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174630</t>
+          <t>175054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3410664</t>
+          <t>3409462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3423719</t>
+          <t>3423723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3383564</t>
+          <t>3383159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3434752</t>
+          <t>3434450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6805136</t>
+          <t>6804712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6856619</t>
+          <t>6855421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667739</t>
+          <t>668265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634227</t>
+          <t>634944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655015</t>
+          <t>655742</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1304794</t>
+          <t>1305607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1328461</t>
+          <t>1328879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49462</t>
+          <t>52399</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>55298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1012842</t>
+          <t>1012571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021248</t>
+          <t>1021514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>993451</t>
+          <t>990514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018996</t>
+          <t>1017225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2010718</t>
+          <t>2010046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2037453</t>
+          <t>2037244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>48037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>751996</t>
+          <t>751689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>739684</t>
+          <t>741012</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764090</t>
+          <t>764577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1497741</t>
+          <t>1496526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523351</t>
+          <t>1521852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19146</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41074</t>
+          <t>41641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928189</t>
+          <t>928534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936562</t>
+          <t>936641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002705</t>
+          <t>1002138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1024633</t>
+          <t>1024680</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1935708</t>
+          <t>1934161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959092</t>
+          <t>1958701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112228</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159314</t>
+          <t>158527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3374298</t>
+          <t>3373801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3388346</t>
+          <t>3387783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3396560</t>
+          <t>3397625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3443443</t>
+          <t>3444532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6779578</t>
+          <t>6780365</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6826664</t>
+          <t>6827373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>31823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49011</t>
+          <t>52003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45499</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57388</t>
+          <t>60037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628723</t>
+          <t>683648</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623743</t>
+          <t>677543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631959</t>
+          <t>686783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>635988</t>
+          <t>691896</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625759</t>
+          <t>680104</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>643914</t>
+          <t>700284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1264713</t>
+          <t>1375543</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1252824</t>
+          <t>1362779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1273474</t>
+          <t>1384976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>36716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49778</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>48441</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>42639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60219</t>
+          <t>65268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1183575</t>
+          <t>1038929</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1176952</t>
+          <t>1031783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1188428</t>
+          <t>1043240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>912787</t>
+          <t>1020043</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>903483</t>
+          <t>1008098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921162</t>
+          <t>1028502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2096363</t>
+          <t>2058972</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2084585</t>
+          <t>2047469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2112438</t>
+          <t>2070098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>953261</t>
+          <t>1065218</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>953261</t>
+          <t>1065218</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>953261</t>
+          <t>1065218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2144804</t>
+          <t>2112737</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2144804</t>
+          <t>2112737</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2144804</t>
+          <t>2112737</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,17 +7255,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>52570</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -7368,17 +7368,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>696936</t>
+          <t>794408</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692039</t>
+          <t>788031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699684</t>
+          <t>797381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>898536</t>
+          <t>771238</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>884126</t>
+          <t>760747</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914746</t>
+          <t>779741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1595472</t>
+          <t>1565646</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1583012</t>
+          <t>1554122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1608504</t>
+          <t>1574477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701168</t>
+          <t>799214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701168</t>
+          <t>799214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701168</t>
+          <t>799214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929773</t>
+          <t>807478</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929773</t>
+          <t>807478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929773</t>
+          <t>807478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1630941</t>
+          <t>1606692</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1630941</t>
+          <t>1606692</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1630941</t>
+          <t>1606692</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26724</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>55148</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62489</t>
+          <t>68583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75605</t>
+          <t>82246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>915231</t>
+          <t>978808</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897907</t>
+          <t>965015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920686</t>
+          <t>984469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1039573</t>
+          <t>1059855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027047</t>
+          <t>1046420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1052147</t>
+          <t>1070008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1954804</t>
+          <t>2038663</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938562</t>
+          <t>2020614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966428</t>
+          <t>2050358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924631</t>
+          <t>987857</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924631</t>
+          <t>987857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924631</t>
+          <t>987857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089536</t>
+          <t>1115003</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089536</t>
+          <t>1115003</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089536</t>
+          <t>1115003</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014167</t>
+          <t>2102860</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014167</t>
+          <t>2102860</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014167</t>
+          <t>2102860</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,22 +7941,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133684</t>
+          <t>156533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182674</t>
+          <t>197422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160015</t>
+          <t>183894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212931</t>
+          <t>231336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8054,27 +8054,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3424466</t>
+          <t>3495792</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3407087</t>
+          <t>3482002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3433058</t>
+          <t>3505280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3486884</t>
+          <t>3543033</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3464666</t>
+          <t>3522384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3513656</t>
+          <t>3563273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6911351</t>
+          <t>7038824</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6887193</t>
+          <t>7013769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6940109</t>
+          <t>7061211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
